--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -421,27 +421,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Číslo mašiny</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Datum provedení prohlídky a rozsah</t>
+          <t>Datum provedení</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Unnamed: 2</t>
+          <t>Provedena prohlídka</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Přístí prohlídka a rozsah</t>
+          <t>Příští prohlídka</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Unnamed: 4</t>
+          <t>Budoucí prohlídka</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -18,7 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -471,30 +475,24 @@
           <t>704020</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-01 00:00:00</t>
-        </is>
+      <c r="B2" s="1" t="n">
+        <v>46235</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-11-01 00:00:00</t>
-        </is>
+      <c r="D2" s="1" t="n">
+        <v>46327</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2027-11-01 00:00:00</t>
-        </is>
+      <c r="F2" s="1" t="n">
+        <v>46692</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -506,30 +504,24 @@
           <t>714226</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
+      <c r="B3" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
+      <c r="D3" s="1" t="n">
+        <v>46266</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2027-06-01 00:00:00</t>
-        </is>
+      <c r="F3" s="1" t="n">
+        <v>46539</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -541,30 +533,24 @@
           <t>814116</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
+      <c r="D4" s="1" t="n">
+        <v>46266</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2028-05-01 00:00:00</t>
-        </is>
+      <c r="F4" s="1" t="n">
+        <v>46874</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -576,30 +562,24 @@
           <t>814002</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
+      <c r="B5" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
+      <c r="D5" s="1" t="n">
+        <v>46266</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2028-03-01 00:00:00</t>
-        </is>
+      <c r="F5" s="1" t="n">
+        <v>46813</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -611,30 +591,24 @@
           <t>814120</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-08-01 00:00:00</t>
-        </is>
+      <c r="B6" s="1" t="n">
+        <v>46235</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-11-01 00:00:00</t>
-        </is>
+      <c r="D6" s="1" t="n">
+        <v>46327</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2028-02-01 00:00:00</t>
-        </is>
+      <c r="F6" s="1" t="n">
+        <v>46784</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -646,30 +620,24 @@
           <t>814062</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-07-01 00:00:00</t>
-        </is>
+      <c r="B7" s="1" t="n">
+        <v>46204</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-10-01 00:00:00</t>
-        </is>
+      <c r="D7" s="1" t="n">
+        <v>46296</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2027-01-01 00:00:00</t>
-        </is>
+      <c r="F7" s="1" t="n">
+        <v>46388</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -681,30 +649,24 @@
           <t>814063</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
+      <c r="B8" s="1" t="n">
+        <v>46266</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-12-01 00:00:00</t>
-        </is>
+      <c r="D8" s="1" t="n">
+        <v>46357</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2027-03-01 00:00:00</t>
-        </is>
+      <c r="F8" s="1" t="n">
+        <v>46447</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -716,30 +678,24 @@
           <t>814077</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2028-07-01 00:00:00</t>
-        </is>
+      <c r="B9" s="1" t="n">
+        <v>46935</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2028-10-01 00:00:00</t>
-        </is>
+      <c r="D9" s="1" t="n">
+        <v>47027</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2025-07-01 00:00:00</t>
-        </is>
+      <c r="F9" s="1" t="n">
+        <v>45839</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -755,30 +711,24 @@
           <t>814091</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-07-01 00:00:00</t>
-        </is>
+      <c r="B10" s="1" t="n">
+        <v>46204</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-10-01 00:00:00</t>
-        </is>
+      <c r="D10" s="1" t="n">
+        <v>46296</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2028-01-01 00:00:00</t>
-        </is>
+      <c r="F10" s="1" t="n">
+        <v>46753</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -790,30 +740,24 @@
           <t>814092</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
+      <c r="B11" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
+      <c r="D11" s="1" t="n">
+        <v>46266</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2028-03-01 00:00:00</t>
-        </is>
+      <c r="F11" s="1" t="n">
+        <v>46813</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -825,30 +769,24 @@
           <t>814093</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
+      <c r="B12" s="1" t="n">
+        <v>46266</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
+      <c r="D12" s="1" t="n">
+        <v>46357</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2027-03-01 00:00:00</t>
-        </is>
+      <c r="F12" s="1" t="n">
+        <v>46447</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -860,30 +798,24 @@
           <t>814020</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-07-01 00:00:00</t>
-        </is>
+      <c r="B13" s="1" t="n">
+        <v>46204</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-10-01 00:00:00</t>
-        </is>
+      <c r="D13" s="1" t="n">
+        <v>46296</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-10-01 00:00:00</t>
-        </is>
+      <c r="F13" s="1" t="n">
+        <v>46296</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -895,30 +827,24 @@
           <t>814137</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-07-01 00:00:00</t>
-        </is>
+      <c r="B14" s="1" t="n">
+        <v>46204</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-10-01 00:00:00</t>
-        </is>
+      <c r="D14" s="1" t="n">
+        <v>46296</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-12-01 00:00:00</t>
-        </is>
+      <c r="F14" s="1" t="n">
+        <v>46357</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -930,30 +856,24 @@
           <t>814143</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
+      <c r="B15" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
+      <c r="D15" s="1" t="n">
+        <v>46266</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2028-03-01 00:00:00</t>
-        </is>
+      <c r="F15" s="1" t="n">
+        <v>46813</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -965,30 +885,24 @@
           <t>814188</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-01 00:00:00</t>
-        </is>
+      <c r="B16" s="1" t="n">
+        <v>46113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-07-01 00:00:00</t>
-        </is>
+      <c r="D16" s="1" t="n">
+        <v>46204</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-01 00:00:00</t>
-        </is>
+      <c r="F16" s="1" t="n">
+        <v>46204</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1004,30 +918,24 @@
           <t>814189</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-08-01 00:00:00</t>
-        </is>
+      <c r="B17" s="1" t="n">
+        <v>46235</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-11-01 00:00:00</t>
-        </is>
+      <c r="D17" s="1" t="n">
+        <v>46327</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-11-01 00:00:00</t>
-        </is>
+      <c r="F17" s="1" t="n">
+        <v>46327</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -1039,30 +947,24 @@
           <t>814190</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-08-01 00:00:00</t>
-        </is>
+      <c r="B18" s="1" t="n">
+        <v>46235</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-11-01 00:00:00</t>
-        </is>
+      <c r="D18" s="1" t="n">
+        <v>46327</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-01 00:00:00</t>
-        </is>
+      <c r="F18" s="1" t="n">
+        <v>46296</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1074,30 +976,24 @@
           <t>814191</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
+      <c r="B19" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
+      <c r="D19" s="1" t="n">
+        <v>46266</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2028-06-01 00:00:00</t>
-        </is>
+      <c r="F19" s="1" t="n">
+        <v>46905</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -1109,30 +1005,24 @@
           <t>814121</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-07-01 00:00:00</t>
-        </is>
+      <c r="B20" s="1" t="n">
+        <v>46204</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-10-01 00:00:00</t>
-        </is>
+      <c r="D20" s="1" t="n">
+        <v>46296</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2028-03-01 00:00:00</t>
-        </is>
+      <c r="F20" s="1" t="n">
+        <v>46813</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1144,30 +1034,24 @@
           <t>814 073</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
+      <c r="B21" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>P-3</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
+      <c r="D21" s="1" t="n">
+        <v>46266</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
+      <c r="F21" s="1" t="n">
+        <v>46266</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1190,32 +1074,32 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Číslo mašiny</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Datum provedení prohlídky a rozsah</t>
+          <t>Datum prohlídky</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Unnamed: 2</t>
+          <t>Provedena prohlídka</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Přístí prohlídka a rozsah</t>
+          <t>Příští prohlídka</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Unnamed: 4</t>
+          <t>Budoucí prohlídka</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:00</t>
+          <t>Typ</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -1225,7 +1109,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>AKTUÁLNÍ PROHLÍDKA</t>
+          <t>Výrobní číslo</t>
         </is>
       </c>
     </row>
@@ -1235,10 +1119,8 @@
           <t>844003</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
+      <c r="B2" s="1" t="n">
+        <v>45992</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1273,10 +1155,8 @@
           <t>844013</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
+      <c r="B3" s="1" t="n">
+        <v>45931</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1311,10 +1191,8 @@
           <t>844014</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>45931</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1349,10 +1227,8 @@
           <t>844015</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
+      <c r="B5" s="1" t="n">
+        <v>45931</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1387,10 +1263,8 @@
           <t>844020</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-01-01 00:00:00</t>
-        </is>
+      <c r="B6" s="1" t="n">
+        <v>46023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1425,10 +1299,8 @@
           <t>844021</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-02-01 00:00:00</t>
-        </is>
+      <c r="B7" s="1" t="n">
+        <v>46054</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1463,10 +1335,8 @@
           <t>844022</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2025-07-01 00:00:00</t>
-        </is>
+      <c r="B8" s="1" t="n">
+        <v>45839</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1501,10 +1371,8 @@
           <t>844025</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-01 00:00:00</t>
-        </is>
+      <c r="B9" s="1" t="n">
+        <v>46143</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,10 +1407,8 @@
           <t>844026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-01 00:00:00</t>
-        </is>
+      <c r="B10" s="1" t="n">
+        <v>46082</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,10 +1443,8 @@
           <t>844027</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-01 00:00:00</t>
-        </is>
+      <c r="B11" s="1" t="n">
+        <v>46143</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,10 +1479,8 @@
           <t>844028</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-05-01 00:00:00</t>
-        </is>
+      <c r="B12" s="1" t="n">
+        <v>46143</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1653,10 +1515,8 @@
           <t>844029</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-02-01 00:00:00</t>
-        </is>
+      <c r="B13" s="1" t="n">
+        <v>46054</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1701,10 +1561,8 @@
           <t>842010</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-01 00:00:00</t>
-        </is>
+      <c r="B15" s="1" t="n">
+        <v>46143</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1739,10 +1597,8 @@
           <t>842011</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2025-11-01 00:00:00</t>
-        </is>
+      <c r="B16" s="1" t="n">
+        <v>45962</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1777,10 +1633,8 @@
           <t>842021</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-08-01 00:00:00</t>
-        </is>
+      <c r="B17" s="1" t="n">
+        <v>46235</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1815,10 +1669,8 @@
           <t>842025</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
+      <c r="B18" s="1" t="n">
+        <v>45992</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1853,10 +1705,8 @@
           <t>842035</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2025-11-01 00:00:00</t>
-        </is>
+      <c r="B19" s="1" t="n">
+        <v>45962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1891,10 +1741,8 @@
           <t>842036</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-01-01 00:00:00</t>
-        </is>
+      <c r="B20" s="1" t="n">
+        <v>46023</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1939,10 +1787,8 @@
           <t>954 210</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
+      <c r="B22" s="1" t="n">
+        <v>45992</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1977,10 +1823,8 @@
           <t>954 211</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-02-01 00:00:00</t>
-        </is>
+      <c r="B23" s="1" t="n">
+        <v>46054</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2015,10 +1859,8 @@
           <t>954 212</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-05-01 00:00:00</t>
-        </is>
+      <c r="B24" s="1" t="n">
+        <v>46143</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2053,10 +1895,8 @@
           <t>954 213</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2025-09-01 00:00:00</t>
-        </is>
+      <c r="B25" s="1" t="n">
+        <v>45901</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2091,10 +1931,8 @@
           <t>954 214</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2025-09-01 00:00:00</t>
-        </is>
+      <c r="B26" s="1" t="n">
+        <v>45901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2129,10 +1967,8 @@
           <t>954 218</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-01 00:00:00</t>
-        </is>
+      <c r="B27" s="1" t="n">
+        <v>46082</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -2193,10 +2029,8 @@
           <t>714 226</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2025-06-22 00:00:00</t>
-        </is>
+      <c r="B2" s="1" t="n">
+        <v>45830</v>
       </c>
     </row>
     <row r="3">
@@ -2205,10 +2039,8 @@
           <t>814 002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025-03-29 00:00:00</t>
-        </is>
+      <c r="B3" s="1" t="n">
+        <v>45745</v>
       </c>
     </row>
     <row r="4">
@@ -2217,10 +2049,8 @@
           <t>814 020</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>45939</v>
       </c>
     </row>
     <row r="5">
@@ -2229,10 +2059,8 @@
           <t>814 062</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2025-03-12 00:00:00</t>
-        </is>
+      <c r="B5" s="1" t="n">
+        <v>45728</v>
       </c>
     </row>
     <row r="6">
@@ -2241,10 +2069,8 @@
           <t>814 063</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2025-03-16 00:00:00</t>
-        </is>
+      <c r="B6" s="1" t="n">
+        <v>45732</v>
       </c>
     </row>
     <row r="7">
@@ -2253,10 +2079,8 @@
           <t>814 091</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2025-04-07 00:00:00</t>
-        </is>
+      <c r="B7" s="1" t="n">
+        <v>45754</v>
       </c>
     </row>
     <row r="8">
@@ -2265,10 +2089,8 @@
           <t>814 092</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
+      <c r="B8" s="1" t="n">
+        <v>45720</v>
       </c>
     </row>
     <row r="9">
@@ -2277,10 +2099,8 @@
           <t>814 093</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2025-03-20 00:00:00</t>
-        </is>
+      <c r="B9" s="1" t="n">
+        <v>45736</v>
       </c>
     </row>
     <row r="10">
@@ -2297,10 +2117,8 @@
           <t>814 118</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2025-05-07 00:00:00</t>
-        </is>
+      <c r="B11" s="1" t="n">
+        <v>45784</v>
       </c>
     </row>
     <row r="12">
@@ -2325,10 +2143,8 @@
           <t>814 137</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2028-04-29 00:00:00</t>
-        </is>
+      <c r="B14" s="1" t="n">
+        <v>46872</v>
       </c>
     </row>
     <row r="15">
@@ -2345,10 +2161,8 @@
           <t>814 188</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2025-03-07 00:00:00</t>
-        </is>
+      <c r="B16" s="1" t="n">
+        <v>45723</v>
       </c>
     </row>
     <row r="17">
@@ -2357,10 +2171,8 @@
           <t>814 189</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2025-05-11 00:00:00</t>
-        </is>
+      <c r="B17" s="1" t="n">
+        <v>45788</v>
       </c>
     </row>
     <row r="18">
@@ -2369,10 +2181,8 @@
           <t>814 190</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2025-04-18 00:00:00</t>
-        </is>
+      <c r="B18" s="1" t="n">
+        <v>45765</v>
       </c>
     </row>
     <row r="19">
@@ -2381,10 +2191,8 @@
           <t>814 191</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2025-05-01 00:00:00</t>
-        </is>
+      <c r="B19" s="1" t="n">
+        <v>45778</v>
       </c>
     </row>
     <row r="20">
@@ -2393,10 +2201,8 @@
           <t>842 010</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2025-04-21 00:00:00</t>
-        </is>
+      <c r="B20" s="1" t="n">
+        <v>45768</v>
       </c>
     </row>
     <row r="21">
@@ -2405,10 +2211,8 @@
           <t>842 011</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2025-05-17 00:00:00</t>
-        </is>
+      <c r="B21" s="1" t="n">
+        <v>45794</v>
       </c>
     </row>
     <row r="22">
@@ -2417,10 +2221,8 @@
           <t>842 021</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2025-04-26 00:00:00</t>
-        </is>
+      <c r="B22" s="1" t="n">
+        <v>45773</v>
       </c>
     </row>
     <row r="23">
@@ -2445,10 +2247,8 @@
           <t>842 036</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2025-05-05 00:00:00</t>
-        </is>
+      <c r="B25" s="1" t="n">
+        <v>45782</v>
       </c>
     </row>
     <row r="26">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -1127,10 +1127,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-12-01 00:00:00</t>
-        </is>
+      <c r="D2" s="1" t="n">
+        <v>46357</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1163,10 +1161,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-10-01 00:00:00</t>
-        </is>
+      <c r="D3" s="1" t="n">
+        <v>46296</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1199,10 +1195,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-10-01 00:00:00</t>
-        </is>
+      <c r="D4" s="1" t="n">
+        <v>46296</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1235,10 +1229,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-10-01 00:00:00</t>
-        </is>
+      <c r="D5" s="1" t="n">
+        <v>46296</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1271,10 +1263,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2027-01-01 00:00:00</t>
-        </is>
+      <c r="D6" s="1" t="n">
+        <v>46388</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1307,10 +1297,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2027-02-01 00:00:00</t>
-        </is>
+      <c r="D7" s="1" t="n">
+        <v>46419</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1343,10 +1331,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-07-01 00:00:00</t>
-        </is>
+      <c r="D8" s="1" t="n">
+        <v>46204</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1379,10 +1365,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2027-05-01 00:00:00</t>
-        </is>
+      <c r="D9" s="1" t="n">
+        <v>46508</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1415,10 +1399,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2027-03-01 00:00:00</t>
-        </is>
+      <c r="D10" s="1" t="n">
+        <v>46447</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1451,10 +1433,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2027-05-01 00:00:00</t>
-        </is>
+      <c r="D11" s="1" t="n">
+        <v>46508</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1487,10 +1467,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2027-05-01 00:00:00</t>
-        </is>
+      <c r="D12" s="1" t="n">
+        <v>46508</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1523,10 +1501,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2027-02-01 00:00:00</t>
-        </is>
+      <c r="D13" s="1" t="n">
+        <v>46419</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1569,10 +1545,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2027-05-01 00:00:00</t>
-        </is>
+      <c r="D15" s="1" t="n">
+        <v>46508</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1605,10 +1579,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-11-01 00:00:00</t>
-        </is>
+      <c r="D16" s="1" t="n">
+        <v>46327</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1641,10 +1613,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2027-08-01 00:00:00</t>
-        </is>
+      <c r="D17" s="1" t="n">
+        <v>46600</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1677,10 +1647,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-12-01 00:00:00</t>
-        </is>
+      <c r="D18" s="1" t="n">
+        <v>46357</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1713,10 +1681,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-11-01 00:00:00</t>
-        </is>
+      <c r="D19" s="1" t="n">
+        <v>46327</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1749,10 +1715,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2027-01-01 00:00:00</t>
-        </is>
+      <c r="D20" s="1" t="n">
+        <v>46388</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1795,10 +1759,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-12-01 00:00:00</t>
-        </is>
+      <c r="D22" s="1" t="n">
+        <v>46357</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1831,10 +1793,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2027-02-01 00:00:00</t>
-        </is>
+      <c r="D23" s="1" t="n">
+        <v>46419</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1867,10 +1827,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2027-05-01 00:00:00</t>
-        </is>
+      <c r="D24" s="1" t="n">
+        <v>46508</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1903,10 +1861,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
+      <c r="D25" s="1" t="n">
+        <v>46266</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1939,10 +1895,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
+      <c r="D26" s="1" t="n">
+        <v>46266</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1975,10 +1929,8 @@
           <t>Pr2</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2027-03-01 00:00:00</t>
-        </is>
+      <c r="D27" s="1" t="n">
+        <v>46447</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P-3</t>
+          <t>P-2</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
@@ -782,7 +782,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P-2</t>
+          <t>P-3</t>
         </is>
       </c>
       <c r="F12" s="1" t="n">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -435,7 +435,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Provedena prohlídka</t>
+          <t>Rozsah</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -445,7 +445,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Budoucí prohlídka</t>
+          <t>Následujcí</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P-2</t>
+          <t>P-3</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Provedena prohlídka</t>
+          <t>Rozsah</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Budoucí prohlídka</t>
+          <t>Následujcí</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P-3</t>
+          <t>P-2</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -534,19 +534,19 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46174</v>
+        <v>46269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>P-3</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46360</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>P-2</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>P-3</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>46296</v>
+        <v>46273</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>46273</v>
+        <v>46296</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>45839</v>
+        <v>46569</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -904,11 +904,7 @@
       <c r="F16" s="1" t="n">
         <v>46204</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Veselí R2</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
     </row>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -991,7 +991,11 @@
       <c r="F19" s="1" t="n">
         <v>46905</v>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Veselí R2</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
     </row>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -886,23 +886,23 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46113</v>
+        <v>46251</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>P-3</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46343</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>P-3</t>
-        </is>
-      </c>
       <c r="F16" s="1" t="n">
-        <v>46204</v>
+        <v>46251</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="F16" s="1" t="n">
-        <v>46251</v>
+        <v>46982</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -1960,7 +1960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1974,6 +1974,11 @@
           <t>Datum provedení</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Příští prohlídka</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1984,6 +1989,9 @@
       <c r="B2" s="1" t="n">
         <v>45830</v>
       </c>
+      <c r="C2" s="1" t="n">
+        <v>46926</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1994,6 +2002,9 @@
       <c r="B3" s="1" t="n">
         <v>45745</v>
       </c>
+      <c r="C3" s="1" t="n">
+        <v>46841</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2004,6 +2015,9 @@
       <c r="B4" s="1" t="n">
         <v>45939</v>
       </c>
+      <c r="C4" s="1" t="n">
+        <v>47035</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2014,6 +2028,9 @@
       <c r="B5" s="1" t="n">
         <v>45728</v>
       </c>
+      <c r="C5" s="1" t="n">
+        <v>46824</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2024,6 +2041,9 @@
       <c r="B6" s="1" t="n">
         <v>45732</v>
       </c>
+      <c r="C6" s="1" t="n">
+        <v>46828</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2034,6 +2054,9 @@
       <c r="B7" s="1" t="n">
         <v>45754</v>
       </c>
+      <c r="C7" s="1" t="n">
+        <v>46850</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2044,6 +2067,9 @@
       <c r="B8" s="1" t="n">
         <v>45720</v>
       </c>
+      <c r="C8" s="1" t="n">
+        <v>46816</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2054,6 +2080,9 @@
       <c r="B9" s="1" t="n">
         <v>45736</v>
       </c>
+      <c r="C9" s="1" t="n">
+        <v>46832</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2062,6 +2091,7 @@
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2072,6 +2102,9 @@
       <c r="B11" s="1" t="n">
         <v>45784</v>
       </c>
+      <c r="C11" s="1" t="n">
+        <v>46880</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2080,6 +2113,7 @@
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2088,6 +2122,7 @@
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2098,6 +2133,9 @@
       <c r="B14" s="1" t="n">
         <v>46872</v>
       </c>
+      <c r="C14" s="1" t="n">
+        <v>47967</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2105,7 +2143,12 @@
           <t>814 143</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" s="1" t="n">
+        <v>45432</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>46527</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2116,6 +2159,9 @@
       <c r="B16" s="1" t="n">
         <v>45723</v>
       </c>
+      <c r="C16" s="1" t="n">
+        <v>46819</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2126,6 +2172,9 @@
       <c r="B17" s="1" t="n">
         <v>45788</v>
       </c>
+      <c r="C17" s="1" t="n">
+        <v>46884</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2136,6 +2185,9 @@
       <c r="B18" s="1" t="n">
         <v>45765</v>
       </c>
+      <c r="C18" s="1" t="n">
+        <v>46861</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2146,6 +2198,9 @@
       <c r="B19" s="1" t="n">
         <v>45778</v>
       </c>
+      <c r="C19" s="1" t="n">
+        <v>46874</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2156,6 +2211,9 @@
       <c r="B20" s="1" t="n">
         <v>45768</v>
       </c>
+      <c r="C20" s="1" t="n">
+        <v>46864</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2166,6 +2224,9 @@
       <c r="B21" s="1" t="n">
         <v>45794</v>
       </c>
+      <c r="C21" s="1" t="n">
+        <v>46890</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2176,6 +2237,9 @@
       <c r="B22" s="1" t="n">
         <v>45773</v>
       </c>
+      <c r="C22" s="1" t="n">
+        <v>46869</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2184,6 +2248,7 @@
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2191,7 +2256,12 @@
           <t>842 035</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" s="1" t="n">
+        <v>44749</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>45845</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2202,6 +2272,9 @@
       <c r="B25" s="1" t="n">
         <v>45782</v>
       </c>
+      <c r="C25" s="1" t="n">
+        <v>46878</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2209,7 +2282,12 @@
           <t>844 003</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" s="1" t="n">
+        <v>45176</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>46272</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2218,6 +2296,7 @@
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2225,7 +2304,12 @@
           <t>844 014</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" s="1" t="n">
+        <v>45140</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>46236</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2234,6 +2318,7 @@
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2241,7 +2326,12 @@
           <t>844 020</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" s="1" t="n">
+        <v>44972</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>46068</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2250,6 +2340,7 @@
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2258,6 +2349,7 @@
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2266,6 +2358,7 @@
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2273,7 +2366,12 @@
           <t>844 026</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" s="1" t="n">
+        <v>44973</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46069</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2282,6 +2380,7 @@
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2290,6 +2389,7 @@
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2298,6 +2398,7 @@
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2306,6 +2407,7 @@
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2314,6 +2416,7 @@
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2322,6 +2425,7 @@
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2330,6 +2434,7 @@
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2338,6 +2443,7 @@
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2346,6 +2452,7 @@
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2357,8 +2357,12 @@
           <t>844 025</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+      <c r="B33" s="1" t="n">
+        <v>45031</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46127</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>45140</v>
+        <v>45797</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46236</v>
+        <v>46893</v>
       </c>
     </row>
     <row r="29">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>44973</v>
+        <v>45716</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46069</v>
+        <v>46811</v>
       </c>
     </row>
     <row r="35">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46174</v>
+        <v>46275</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>P-3</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46366</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>P-2</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>P-3</t>
         </is>
       </c>
       <c r="F11" s="1" t="n">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2295,8 +2295,12 @@
           <t>844 013</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+      <c r="B27" s="1" t="n">
+        <v>45577</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>46672</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2317,8 +2321,12 @@
           <t>844 015</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+      <c r="B29" s="1" t="n">
+        <v>45184</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>46280</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2247,8 +2247,12 @@
           <t>842 025</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="B23" s="1" t="n">
+        <v>45041</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>46137</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2347,8 +2351,12 @@
           <t>844 021</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+      <c r="B31" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>46445</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2356,8 +2364,12 @@
           <t>844 022</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+      <c r="B32" s="1" t="n">
+        <v>45421</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>46516</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2403,8 +2403,12 @@
           <t>844 027</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+      <c r="B35" s="1" t="n">
+        <v>45158</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46254</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2412,8 +2416,12 @@
           <t>844 028</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+      <c r="B36" s="1" t="n">
+        <v>44989</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46085</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2421,8 +2429,12 @@
           <t>844 029</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+      <c r="B37" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46364</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2478,8 +2478,12 @@
           <t>954 214</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+      <c r="B42" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>47099</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2442,8 +2442,12 @@
           <t>954 210</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="B38" s="1" t="n">
+        <v>45586</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>46681</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2451,8 +2455,12 @@
           <t>954 211</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+      <c r="B39" s="1" t="n">
+        <v>45395</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>46490</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2460,8 +2468,12 @@
           <t>954 212</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+      <c r="B40" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>47260</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2469,8 +2481,12 @@
           <t>954 213</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+      <c r="B41" s="1" t="n">
+        <v>45256</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>46352</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2491,8 +2507,12 @@
           <t>954 218</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
+      <c r="B43" s="1" t="n">
+        <v>45686</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>46781</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>45768</v>
+        <v>46161</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46864</v>
+        <v>47257</v>
       </c>
     </row>
     <row r="21">
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>45794</v>
+        <v>45793</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46890</v>
+        <v>46889</v>
       </c>
     </row>
     <row r="22">
@@ -2248,10 +2248,10 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>45041</v>
+        <v>45791</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46137</v>
+        <v>46887</v>
       </c>
     </row>
     <row r="24">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44749</v>
+        <v>45791</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45845</v>
+        <v>46887</v>
       </c>
     </row>
     <row r="25">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -1960,7 +1960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2514,6 +2514,19 @@
         <v>46781</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>704 020</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>47056</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2090,8 +2090,12 @@
           <t>814 116</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" s="1" t="n">
+        <v>44940</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>46036</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2112,8 +2116,12 @@
           <t>814 120</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" s="1" t="n">
+        <v>45135</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>46231</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/prohlidky.xlsx
+++ b/prohlidky.xlsx
@@ -2129,8 +2129,12 @@
           <t>814 121</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="B13" s="1" t="n">
+        <v>45398</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>46493</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
